--- a/www_Test _new_lot_rull/fill/dayreport.xlsx
+++ b/www_Test _new_lot_rull/fill/dayreport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="0" sheetId="1" r:id="rId4"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>(附件-2)</t>
   </si>
@@ -35,7 +35,7 @@
     <t>No.1</t>
   </si>
   <si>
-    <t>2024年06月01日</t>
+    <t>2024年10月21日</t>
   </si>
   <si>
     <t>充填日期</t>
@@ -77,88 +77,67 @@
     <t>荷姿</t>
   </si>
   <si>
-    <t>2024/06/01</t>
+    <t>2024/10/21</t>
   </si>
   <si>
     <t>H2SO4</t>
   </si>
   <si>
-    <t>L008</t>
+    <t>L052</t>
   </si>
   <si>
-    <t>10560 L</t>
+    <t>10730 L</t>
   </si>
   <si>
     <t>PFA</t>
   </si>
   <si>
-    <t>S624F01</t>
+    <t>S624X21</t>
   </si>
   <si>
-    <t>台積F18-P6A</t>
+    <t>台積F15-P4</t>
   </si>
   <si>
     <t>PE</t>
   </si>
   <si>
-    <t>L020</t>
+    <t>LP12</t>
   </si>
   <si>
-    <t>10750 L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">台積F15-P3  </t>
-  </si>
-  <si>
-    <t>L034</t>
-  </si>
-  <si>
-    <t>10650 L</t>
-  </si>
-  <si>
-    <t>台積F18-P2B</t>
-  </si>
-  <si>
-    <t>L047</t>
-  </si>
-  <si>
-    <t>台積F15-P4</t>
-  </si>
-  <si>
-    <t>L607</t>
-  </si>
-  <si>
-    <t>6460 L</t>
-  </si>
-  <si>
-    <t>台積F12-P2</t>
-  </si>
-  <si>
-    <t>L619</t>
-  </si>
-  <si>
-    <t>6000 L</t>
-  </si>
-  <si>
-    <t>台灣美光</t>
-  </si>
-  <si>
-    <t>L620</t>
-  </si>
-  <si>
-    <t>5800 L</t>
-  </si>
-  <si>
-    <t>台積電F120</t>
-  </si>
-  <si>
-    <t>LK26</t>
-  </si>
-  <si>
-    <t>5700 L</t>
+    <t>6440 L</t>
   </si>
   <si>
     <t>義鎧科技</t>
+  </si>
+  <si>
+    <t>LP64</t>
+  </si>
+  <si>
+    <t>L102</t>
+  </si>
+  <si>
+    <t>860 L</t>
+  </si>
+  <si>
+    <t>S924X21</t>
+  </si>
+  <si>
+    <t>力積電8B</t>
+  </si>
+  <si>
+    <t>3MAE</t>
+  </si>
+  <si>
+    <t>L005</t>
+  </si>
+  <si>
+    <t>0 L</t>
+  </si>
+  <si>
+    <t>M424X21</t>
+  </si>
+  <si>
+    <t>台塑勝高</t>
   </si>
   <si>
     <t>充填G</t>
@@ -180,27 +159,6 @@
   </si>
   <si>
     <t>No.2</t>
-  </si>
-  <si>
-    <t>LP25</t>
-  </si>
-  <si>
-    <t>5240 L</t>
-  </si>
-  <si>
-    <t>LP55</t>
-  </si>
-  <si>
-    <t>5270 L</t>
-  </si>
-  <si>
-    <t>LP56</t>
-  </si>
-  <si>
-    <t>LP59</t>
-  </si>
-  <si>
-    <t>5680 L</t>
   </si>
   <si>
     <t>No.3</t>
@@ -787,7 +745,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>22</v>
@@ -833,7 +791,7 @@
         <v>21</v>
       </c>
       <c r="H7" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>22</v>
@@ -854,7 +812,7 @@
         <v>24</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -871,7 +829,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -879,13 +837,13 @@
         <v>21</v>
       </c>
       <c r="H9" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K9" s="5"/>
     </row>
@@ -900,7 +858,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -914,10 +872,10 @@
         <v>18</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -925,10 +883,10 @@
         <v>21</v>
       </c>
       <c r="H11" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>32</v>
@@ -957,13 +915,13 @@
         <v>17</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -971,13 +929,13 @@
         <v>21</v>
       </c>
       <c r="H13" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K13" s="5"/>
     </row>
@@ -999,32 +957,16 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="3">
-        <v>7</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:12">
@@ -1034,43 +976,23 @@
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3">
-        <v>1</v>
-      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="3">
-        <v>10</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
     <row r="18" spans="1:12">
@@ -1080,43 +1002,23 @@
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="3">
-        <v>4</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:12">
@@ -1126,12 +1028,8 @@
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -1157,19 +1055,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1200,7 +1098,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -1347,7 +1245,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -1648,19 +1546,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1691,7 +1589,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -1838,7 +1736,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -1852,9 +1750,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
-      <c r="I2" s="10" t="s">
-        <v>3</v>
-      </c>
+      <c r="I2" s="10"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
     </row>
@@ -1913,32 +1809,16 @@
       <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="3">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="17.25">
@@ -1948,43 +1828,23 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="3">
-        <v>4</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:12">
@@ -1994,43 +1854,23 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:12">
@@ -2040,43 +1880,23 @@
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="3">
-        <v>4</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:12">
@@ -2086,12 +1906,8 @@
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -2221,19 +2037,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2264,7 +2080,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -2411,7 +2227,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -2712,19 +2528,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2755,7 +2571,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -2902,7 +2718,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -3203,19 +3019,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3246,7 +3062,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -3393,7 +3209,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -3694,19 +3510,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3737,7 +3553,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -3884,7 +3700,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -4185,19 +4001,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4228,7 +4044,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -4375,7 +4191,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -4676,19 +4492,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4719,7 +4535,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -4866,7 +4682,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -5167,19 +4983,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -5210,7 +5026,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -5357,7 +5173,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="9" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -5658,19 +5474,19 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -5701,7 +5517,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="J25" s="11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K25" s="11"/>
     </row>
